--- a/research/traditional_assets/database/data/togo/togo_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/togo/togo_bank_money_center.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0182</v>
+        <v>0.108</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,82 +603,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>235.6</v>
+        <v>300.8</v>
       </c>
       <c r="L2">
-        <v>0.1334163882439549</v>
+        <v>0.1588760365499392</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>46.91</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04406349802742815</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.1559507978723405</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>39.6</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.03719706932181101</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.1316489361702128</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>7.310000000000002</v>
+      </c>
+      <c r="T2">
+        <v>0.1558303133660201</v>
       </c>
       <c r="U2">
-        <v>2480.6</v>
+        <v>3131.6</v>
       </c>
       <c r="V2">
-        <v>2.324835988753514</v>
+        <v>2.94157430020665</v>
       </c>
       <c r="W2">
-        <v>0.126607764724327</v>
+        <v>0.1502589696918724</v>
       </c>
       <c r="X2">
-        <v>0.2428094740150396</v>
+        <v>0.2174098755517131</v>
       </c>
       <c r="Y2">
-        <v>-0.1162017092907126</v>
+        <v>-0.06715090585984065</v>
       </c>
       <c r="Z2">
-        <v>0.8190250916005751</v>
+        <v>0.6656236816200255</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1149368922114228</v>
+        <v>0.1505684189396293</v>
       </c>
       <c r="AC2">
-        <v>-0.1149368922114228</v>
+        <v>-0.1505684189396293</v>
       </c>
       <c r="AD2">
-        <v>3689.2</v>
+        <v>2037.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3689.2</v>
+        <v>2037.8</v>
       </c>
       <c r="AG2">
-        <v>1208.6</v>
+        <v>-1093.8</v>
       </c>
       <c r="AH2">
-        <v>0.7756612421681174</v>
+        <v>0.6568463125322331</v>
       </c>
       <c r="AI2">
-        <v>0.6067563566987928</v>
+        <v>0.5408748274763775</v>
       </c>
       <c r="AJ2">
-        <v>0.5311126735805941</v>
+        <v>37.45890410958898</v>
       </c>
       <c r="AK2">
-        <v>0.3357595288365374</v>
+        <v>-1.719811320754717</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -716,10 +719,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>17.4</v>
+        <v>24.9</v>
       </c>
       <c r="L3">
-        <v>0.07084690553745927</v>
+        <v>0.09826361483820047</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,49 +752,43 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.09513395297977036</v>
+        <v>0.1244377811094453</v>
       </c>
       <c r="X3">
-        <v>0.1895817335192664</v>
+        <v>0.1147453831983383</v>
       </c>
       <c r="Y3">
-        <v>-0.094447780539496</v>
+        <v>0.009692397911106945</v>
       </c>
       <c r="Z3">
-        <v>0.152518164317208</v>
+        <v>0.1850310332238043</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1031255600368796</v>
+        <v>0.1147453831983383</v>
       </c>
       <c r="AC3">
-        <v>-0.1031255600368796</v>
+        <v>-0.1147453831983383</v>
       </c>
       <c r="AD3">
-        <v>1300.6</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1300.6</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1300.6</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.7033311702357776</v>
-      </c>
-      <c r="AI3">
-        <v>0.8284076433121018</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.7033311702357776</v>
-      </c>
-      <c r="AK3">
-        <v>0.8284076433121018</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -817,7 +814,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0182</v>
+        <v>0.108</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -832,82 +829,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>218.2</v>
+        <v>275.9</v>
       </c>
       <c r="L4">
-        <v>0.1435243044136026</v>
+        <v>0.1682419659735349</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>46.91</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.08062908215881748</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.1700253715114172</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>39.6</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.06806462701959437</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.1435302645886191</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>7.310000000000002</v>
+      </c>
+      <c r="T4">
+        <v>0.1558303133660201</v>
       </c>
       <c r="U4">
-        <v>2480.6</v>
+        <v>3131.6</v>
       </c>
       <c r="V4">
-        <v>4.785108024691358</v>
+        <v>5.382605706428326</v>
       </c>
       <c r="W4">
-        <v>0.1580815764688836</v>
+        <v>0.1760801582742995</v>
       </c>
       <c r="X4">
-        <v>0.2960372145108128</v>
+        <v>0.3200743679050878</v>
       </c>
       <c r="Y4">
-        <v>-0.1379556380419292</v>
+        <v>-0.1439942096307883</v>
       </c>
       <c r="Z4">
-        <v>2.785452546720412</v>
+        <v>1.111871991321445</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.126748224385966</v>
+        <v>0.1863914546809203</v>
       </c>
       <c r="AC4">
-        <v>-0.126748224385966</v>
+        <v>-0.1863914546809203</v>
       </c>
       <c r="AD4">
-        <v>2388.6</v>
+        <v>2037.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2388.6</v>
+        <v>2037.8</v>
       </c>
       <c r="AG4">
-        <v>-92</v>
+        <v>-1093.8</v>
       </c>
       <c r="AH4">
-        <v>0.821671826625387</v>
+        <v>0.7779050236677355</v>
       </c>
       <c r="AI4">
-        <v>0.5295995742982573</v>
+        <v>0.5408748274763775</v>
       </c>
       <c r="AJ4">
-        <v>-0.2157598499061914</v>
+        <v>2.136328125</v>
       </c>
       <c r="AK4">
-        <v>-0.04532912889239259</v>
+        <v>-1.719811320754717</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/togo/togo_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/togo/togo_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,7 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.108</v>
+        <v>0.028</v>
+      </c>
+      <c r="E2">
+        <v>0.08</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>300.8</v>
+        <v>314.3</v>
       </c>
       <c r="L2">
-        <v>0.1588760365499392</v>
+        <v>0.1812781174299227</v>
       </c>
       <c r="M2">
-        <v>46.91</v>
+        <v>34.5</v>
       </c>
       <c r="N2">
-        <v>0.04406349802742815</v>
+        <v>0.05966793497059841</v>
       </c>
       <c r="O2">
-        <v>0.1559507978723405</v>
+        <v>0.1097677378300986</v>
       </c>
       <c r="P2">
-        <v>39.6</v>
+        <v>34.5</v>
       </c>
       <c r="Q2">
-        <v>0.03719706932181101</v>
+        <v>0.05966793497059841</v>
       </c>
       <c r="R2">
-        <v>0.1316489361702128</v>
+        <v>0.1097677378300986</v>
       </c>
       <c r="S2">
-        <v>7.310000000000002</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1558303133660201</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>3131.6</v>
+        <v>3112</v>
       </c>
       <c r="V2">
-        <v>2.94157430020665</v>
+        <v>5.382220684884123</v>
       </c>
       <c r="W2">
-        <v>0.1502589696918724</v>
+        <v>0.2543703463904176</v>
       </c>
       <c r="X2">
-        <v>0.2174098755517131</v>
+        <v>0.2582799947637283</v>
       </c>
       <c r="Y2">
-        <v>-0.06715090585984065</v>
+        <v>-0.003909648373310703</v>
       </c>
       <c r="Z2">
-        <v>0.6656236816200255</v>
+        <v>12.22708039492245</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1505684189396293</v>
+        <v>0.1462464962185223</v>
       </c>
       <c r="AC2">
-        <v>-0.1505684189396293</v>
+        <v>-0.1462464962185223</v>
       </c>
       <c r="AD2">
-        <v>2037.8</v>
+        <v>2334.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2037.8</v>
+        <v>2334.3</v>
       </c>
       <c r="AG2">
-        <v>-1093.8</v>
+        <v>-777.6999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.6568463125322331</v>
+        <v>0.8014763948497855</v>
       </c>
       <c r="AI2">
-        <v>0.5408748274763775</v>
+        <v>0.5750923872875093</v>
       </c>
       <c r="AJ2">
-        <v>37.45890410958898</v>
+        <v>3.898245614035091</v>
       </c>
       <c r="AK2">
-        <v>-1.719811320754717</v>
+        <v>-0.821224920802534</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -698,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oragroup SA (BRVM:ORGT)</t>
+          <t>Ecobank Transnational Incorporated (NGSE:ETI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -706,6 +709,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.028</v>
+      </c>
+      <c r="E3">
+        <v>0.08</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -719,200 +728,90 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>24.9</v>
+        <v>314.3</v>
       </c>
       <c r="L3">
-        <v>0.09826361483820047</v>
+        <v>0.1812781174299227</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>34.5</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05966793497059841</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1097677378300986</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>34.5</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05966793497059841</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1097677378300986</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0</v>
+        <v>3112</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>5.382220684884123</v>
       </c>
       <c r="W3">
-        <v>0.1244377811094453</v>
+        <v>0.2543703463904176</v>
       </c>
       <c r="X3">
-        <v>0.1147453831983383</v>
+        <v>0.2582799947637283</v>
       </c>
       <c r="Y3">
-        <v>0.009692397911106945</v>
+        <v>-0.003909648373310703</v>
       </c>
       <c r="Z3">
-        <v>0.1850310332238043</v>
+        <v>12.22708039492245</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1147453831983383</v>
+        <v>0.1462464962185223</v>
       </c>
       <c r="AC3">
-        <v>-0.1147453831983383</v>
+        <v>-0.1462464962185223</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2334.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2334.3</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-777.6999999999998</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.8014763948497855</v>
+      </c>
+      <c r="AI3">
+        <v>0.5750923872875093</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>3.898245614035091</v>
+      </c>
+      <c r="AK3">
+        <v>-0.821224920802534</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Togo</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ecobank Transnational Incorporated (NGSE:ETI)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.108</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>275.9</v>
-      </c>
-      <c r="L4">
-        <v>0.1682419659735349</v>
-      </c>
-      <c r="M4">
-        <v>46.91</v>
-      </c>
-      <c r="N4">
-        <v>0.08062908215881748</v>
-      </c>
-      <c r="O4">
-        <v>0.1700253715114172</v>
-      </c>
-      <c r="P4">
-        <v>39.6</v>
-      </c>
-      <c r="Q4">
-        <v>0.06806462701959437</v>
-      </c>
-      <c r="R4">
-        <v>0.1435302645886191</v>
-      </c>
-      <c r="S4">
-        <v>7.310000000000002</v>
-      </c>
-      <c r="T4">
-        <v>0.1558303133660201</v>
-      </c>
-      <c r="U4">
-        <v>3131.6</v>
-      </c>
-      <c r="V4">
-        <v>5.382605706428326</v>
-      </c>
-      <c r="W4">
-        <v>0.1760801582742995</v>
-      </c>
-      <c r="X4">
-        <v>0.3200743679050878</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1439942096307883</v>
-      </c>
-      <c r="Z4">
-        <v>1.111871991321445</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.1863914546809203</v>
-      </c>
-      <c r="AC4">
-        <v>-0.1863914546809203</v>
-      </c>
-      <c r="AD4">
-        <v>2037.8</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>2037.8</v>
-      </c>
-      <c r="AG4">
-        <v>-1093.8</v>
-      </c>
-      <c r="AH4">
-        <v>0.7779050236677355</v>
-      </c>
-      <c r="AI4">
-        <v>0.5408748274763775</v>
-      </c>
-      <c r="AJ4">
-        <v>2.136328125</v>
-      </c>
-      <c r="AK4">
-        <v>-1.719811320754717</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/togo/togo_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/togo/togo_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.028</v>
+        <v>0.0457</v>
       </c>
       <c r="E2">
-        <v>0.08</v>
+        <v>0.162</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>314.3</v>
+        <v>295.7</v>
       </c>
       <c r="L2">
-        <v>0.1812781174299227</v>
+        <v>0.1674974510026056</v>
       </c>
       <c r="M2">
-        <v>34.5</v>
+        <v>7.31</v>
       </c>
       <c r="N2">
-        <v>0.05966793497059841</v>
+        <v>0.01635712687402103</v>
       </c>
       <c r="O2">
-        <v>0.1097677378300986</v>
+        <v>0.02472100101454177</v>
       </c>
       <c r="P2">
-        <v>34.5</v>
+        <v>7.31</v>
       </c>
       <c r="Q2">
-        <v>0.05966793497059841</v>
+        <v>0.01635712687402103</v>
       </c>
       <c r="R2">
-        <v>0.1097677378300986</v>
+        <v>0.02472100101454177</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3112</v>
+        <v>3798.4</v>
       </c>
       <c r="V2">
-        <v>5.382220684884123</v>
+        <v>8.499440590736183</v>
       </c>
       <c r="W2">
-        <v>0.2543703463904176</v>
+        <v>0.2567285987150547</v>
       </c>
       <c r="X2">
-        <v>0.2582799947637283</v>
+        <v>0.2925337090147482</v>
       </c>
       <c r="Y2">
-        <v>-0.003909648373310703</v>
+        <v>-0.03580511029969352</v>
       </c>
       <c r="Z2">
-        <v>12.22708039492245</v>
+        <v>4.719059075113601</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1462464962185223</v>
+        <v>0.1417791031825109</v>
       </c>
       <c r="AC2">
-        <v>-0.1462464962185223</v>
+        <v>-0.1417791031825109</v>
       </c>
       <c r="AD2">
-        <v>2334.3</v>
+        <v>2333.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2334.3</v>
+        <v>2333.5</v>
       </c>
       <c r="AG2">
-        <v>-777.6999999999998</v>
+        <v>-1464.9</v>
       </c>
       <c r="AH2">
-        <v>0.8014763948497855</v>
+        <v>0.839267731261689</v>
       </c>
       <c r="AI2">
-        <v>0.5750923872875093</v>
+        <v>0.5906548206646923</v>
       </c>
       <c r="AJ2">
-        <v>3.898245614035091</v>
+        <v>1.438998035363458</v>
       </c>
       <c r="AK2">
-        <v>-0.821224920802534</v>
+        <v>-9.618516086671047</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.028</v>
+        <v>0.0457</v>
       </c>
       <c r="E3">
-        <v>0.08</v>
+        <v>0.162</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>314.3</v>
+        <v>295.7</v>
       </c>
       <c r="L3">
-        <v>0.1812781174299227</v>
+        <v>0.1674974510026056</v>
       </c>
       <c r="M3">
-        <v>34.5</v>
+        <v>7.31</v>
       </c>
       <c r="N3">
-        <v>0.05966793497059841</v>
+        <v>0.01635712687402103</v>
       </c>
       <c r="O3">
-        <v>0.1097677378300986</v>
+        <v>0.02472100101454177</v>
       </c>
       <c r="P3">
-        <v>34.5</v>
+        <v>7.31</v>
       </c>
       <c r="Q3">
-        <v>0.05966793497059841</v>
+        <v>0.01635712687402103</v>
       </c>
       <c r="R3">
-        <v>0.1097677378300986</v>
+        <v>0.02472100101454177</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3112</v>
+        <v>3798.4</v>
       </c>
       <c r="V3">
-        <v>5.382220684884123</v>
+        <v>8.499440590736183</v>
       </c>
       <c r="W3">
-        <v>0.2543703463904176</v>
+        <v>0.2567285987150547</v>
       </c>
       <c r="X3">
-        <v>0.2582799947637283</v>
+        <v>0.2925337090147482</v>
       </c>
       <c r="Y3">
-        <v>-0.003909648373310703</v>
+        <v>-0.03580511029969352</v>
       </c>
       <c r="Z3">
-        <v>12.22708039492245</v>
+        <v>4.719059075113601</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1462464962185223</v>
+        <v>0.1417791031825109</v>
       </c>
       <c r="AC3">
-        <v>-0.1462464962185223</v>
+        <v>-0.1417791031825109</v>
       </c>
       <c r="AD3">
-        <v>2334.3</v>
+        <v>2333.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2334.3</v>
+        <v>2333.5</v>
       </c>
       <c r="AG3">
-        <v>-777.6999999999998</v>
+        <v>-1464.9</v>
       </c>
       <c r="AH3">
-        <v>0.8014763948497855</v>
+        <v>0.839267731261689</v>
       </c>
       <c r="AI3">
-        <v>0.5750923872875093</v>
+        <v>0.5906548206646923</v>
       </c>
       <c r="AJ3">
-        <v>3.898245614035091</v>
+        <v>1.438998035363458</v>
       </c>
       <c r="AK3">
-        <v>-0.821224920802534</v>
+        <v>-9.618516086671047</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/togo/togo_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/togo/togo_bank_money_center.xlsx
@@ -645,10 +645,10 @@
         <v>0.2567285987150547</v>
       </c>
       <c r="X2">
-        <v>0.2925337090147482</v>
+        <v>0.2925607889755133</v>
       </c>
       <c r="Y2">
-        <v>-0.03580511029969352</v>
+        <v>-0.03583219026045859</v>
       </c>
       <c r="Z2">
         <v>4.719059075113601</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1417791031825109</v>
+        <v>0.141783455806042</v>
       </c>
       <c r="AC2">
-        <v>-0.1417791031825109</v>
+        <v>-0.141783455806042</v>
       </c>
       <c r="AD2">
         <v>2333.5</v>
@@ -767,10 +767,10 @@
         <v>0.2567285987150547</v>
       </c>
       <c r="X3">
-        <v>0.2925337090147482</v>
+        <v>0.2925607889755133</v>
       </c>
       <c r="Y3">
-        <v>-0.03580511029969352</v>
+        <v>-0.03583219026045859</v>
       </c>
       <c r="Z3">
         <v>4.719059075113601</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1417791031825109</v>
+        <v>0.141783455806042</v>
       </c>
       <c r="AC3">
-        <v>-0.1417791031825109</v>
+        <v>-0.141783455806042</v>
       </c>
       <c r="AD3">
         <v>2333.5</v>
